--- a/corpus/C01.xlsx
+++ b/corpus/C01.xlsx
@@ -759,69 +759,68 @@
         <f>I9</f>
         <v>15351.0</v>
       </c>
-      <c r="K5">
-        <f>J9</f>
-        <v>16367.0</v>
+      <c r="K5" t="n">
+        <v>9800</v>
       </c>
       <c r="L5">
         <f>K9</f>
-        <v>17451.0</v>
+        <v>10449.0</v>
       </c>
       <c r="M5">
         <f>L9</f>
-        <v>18606.0</v>
+        <v>11141.0</v>
       </c>
       <c r="N5">
         <f>M9</f>
-        <v>19838.0</v>
+        <v>11879.0</v>
       </c>
       <c r="O5">
         <f>N9</f>
-        <v>21152.0</v>
+        <v>12666.0</v>
       </c>
       <c r="P5">
         <f>O9</f>
-        <v>22552.0</v>
+        <v>13504.0</v>
       </c>
       <c r="Q5">
         <f>P9</f>
-        <v>24045.0</v>
+        <v>14398.0</v>
       </c>
       <c r="R5">
         <f>Q9</f>
-        <v>25637.0</v>
+        <v>15351.0</v>
       </c>
       <c r="S5">
         <f>R9</f>
-        <v>27334.0</v>
+        <v>16367.0</v>
       </c>
       <c r="T5">
         <f>S9</f>
-        <v>29144.0</v>
+        <v>17451.0</v>
       </c>
       <c r="U5">
         <f>T9</f>
-        <v>31074.0</v>
+        <v>18606.0</v>
       </c>
       <c r="V5">
         <f>U9</f>
-        <v>33131.0</v>
+        <v>19838.0</v>
       </c>
       <c r="W5">
         <f>V9</f>
-        <v>35325.0</v>
+        <v>21152.0</v>
       </c>
       <c r="X5">
         <f>W9</f>
-        <v>37664.0</v>
+        <v>22552.0</v>
       </c>
       <c r="Y5">
         <f>X9</f>
-        <v>40157.0</v>
+        <v>24045.0</v>
       </c>
       <c r="Z5">
         <f>Y9</f>
-        <v>42815.0</v>
+        <v>25637.0</v>
       </c>
     </row>
     <row r="6">
@@ -864,67 +863,67 @@
       </c>
       <c r="K6">
         <f>ROUND(K5*Assumptions!$B$5,0)</f>
-        <v>1462.0</v>
+        <v>875.0</v>
       </c>
       <c r="L6">
         <f>ROUND(L5*Assumptions!$B$5,0)</f>
-        <v>1558.0</v>
+        <v>933.0</v>
       </c>
       <c r="M6">
         <f>ROUND(M5*Assumptions!$B$5,0)</f>
-        <v>1662.0</v>
+        <v>995.0</v>
       </c>
       <c r="N6">
         <f>ROUND(N5*Assumptions!$B$5,0)</f>
-        <v>1772.0</v>
+        <v>1061.0</v>
       </c>
       <c r="O6">
         <f>ROUND(O5*Assumptions!$B$5,0)</f>
-        <v>1889.0</v>
+        <v>1131.0</v>
       </c>
       <c r="P6">
         <f>ROUND(P5*Assumptions!$B$5,0)</f>
-        <v>2014.0</v>
+        <v>1206.0</v>
       </c>
       <c r="Q6">
         <f>ROUND(Q5*Assumptions!$B$5,0)</f>
-        <v>2147.0</v>
+        <v>1286.0</v>
       </c>
       <c r="R6">
         <f>ROUND(R5*Assumptions!$B$5,0)</f>
-        <v>2289.0</v>
+        <v>1371.0</v>
       </c>
       <c r="S6">
         <f>ROUND(S5*Assumptions!$B$5,0)</f>
-        <v>2441.0</v>
+        <v>1462.0</v>
       </c>
       <c r="T6">
         <f>ROUND(T5*Assumptions!$B$5,0)</f>
-        <v>2603.0</v>
+        <v>1558.0</v>
       </c>
       <c r="U6">
         <f>ROUND(U5*Assumptions!$B$5,0)</f>
-        <v>2775.0</v>
+        <v>1662.0</v>
       </c>
       <c r="V6">
         <f>ROUND(V5*Assumptions!$B$5,0)</f>
-        <v>2959.0</v>
+        <v>1772.0</v>
       </c>
       <c r="W6">
         <f>ROUND(W5*Assumptions!$B$5,0)</f>
-        <v>3155.0</v>
+        <v>1889.0</v>
       </c>
       <c r="X6">
         <f>ROUND(X5*Assumptions!$B$5,0)</f>
-        <v>3363.0</v>
+        <v>2014.0</v>
       </c>
       <c r="Y6">
         <f>ROUND(Y5*Assumptions!$B$5,0)</f>
-        <v>3586.0</v>
+        <v>2147.0</v>
       </c>
       <c r="Z6">
         <f>ROUND(Z5*Assumptions!$B$5,0)</f>
-        <v>3823.0</v>
+        <v>2289.0</v>
       </c>
     </row>
     <row r="7">
@@ -967,67 +966,67 @@
       </c>
       <c r="K7">
         <f>-ROUND(K5*Assumptions!$B$6,0)</f>
-        <v>-378.0</v>
+        <v>-226.0</v>
       </c>
       <c r="L7">
         <f>-ROUND(L5*Assumptions!$B$6,0)</f>
-        <v>-403.0</v>
+        <v>-241.0</v>
       </c>
       <c r="M7">
         <f>-ROUND(M5*Assumptions!$B$6,0)</f>
-        <v>-430.0</v>
+        <v>-257.0</v>
       </c>
       <c r="N7">
         <f>-ROUND(N5*Assumptions!$B$6,0)</f>
-        <v>-458.0</v>
+        <v>-274.0</v>
       </c>
       <c r="O7">
         <f>-ROUND(O5*Assumptions!$B$6,0)</f>
-        <v>-489.0</v>
+        <v>-293.0</v>
       </c>
       <c r="P7">
         <f>-ROUND(P5*Assumptions!$B$6,0)</f>
-        <v>-521.0</v>
+        <v>-312.0</v>
       </c>
       <c r="Q7">
         <f>-ROUND(Q5*Assumptions!$B$6,0)</f>
-        <v>-555.0</v>
+        <v>-333.0</v>
       </c>
       <c r="R7">
         <f>-ROUND(R5*Assumptions!$B$6,0)</f>
-        <v>-592.0</v>
+        <v>-355.0</v>
       </c>
       <c r="S7">
         <f>-ROUND(S5*Assumptions!$B$6,0)</f>
-        <v>-631.0</v>
+        <v>-378.0</v>
       </c>
       <c r="T7">
         <f>-ROUND(T5*Assumptions!$B$6,0)</f>
-        <v>-673.0</v>
+        <v>-403.0</v>
       </c>
       <c r="U7">
         <f>-ROUND(U5*Assumptions!$B$6,0)</f>
-        <v>-718.0</v>
+        <v>-430.0</v>
       </c>
       <c r="V7">
         <f>-ROUND(V5*Assumptions!$B$6,0)</f>
-        <v>-765.0</v>
+        <v>-458.0</v>
       </c>
       <c r="W7">
         <f>-ROUND(W5*Assumptions!$B$6,0)</f>
-        <v>-816.0</v>
+        <v>-489.0</v>
       </c>
       <c r="X7">
         <f>-ROUND(X5*Assumptions!$B$6,0)</f>
-        <v>-870.0</v>
+        <v>-521.0</v>
       </c>
       <c r="Y7">
         <f>-ROUND(Y5*Assumptions!$B$6,0)</f>
-        <v>-928.0</v>
+        <v>-555.0</v>
       </c>
       <c r="Z7">
         <f>-ROUND(Z5*Assumptions!$B$6,0)</f>
-        <v>-989.0</v>
+        <v>-592.0</v>
       </c>
     </row>
     <row r="9">
@@ -1070,67 +1069,67 @@
       </c>
       <c r="K9">
         <f>K5+K6+K7</f>
-        <v>17451.0</v>
+        <v>10449.0</v>
       </c>
       <c r="L9">
         <f>L5+L6+L7</f>
-        <v>18606.0</v>
+        <v>11141.0</v>
       </c>
       <c r="M9">
         <f>M5+M6+M7</f>
-        <v>19838.0</v>
+        <v>11879.0</v>
       </c>
       <c r="N9">
         <f>N5+N6+N7</f>
-        <v>21152.0</v>
+        <v>12666.0</v>
       </c>
       <c r="O9">
         <f>O5+O6+O7</f>
-        <v>22552.0</v>
+        <v>13504.0</v>
       </c>
       <c r="P9">
         <f>P5+P6+P7</f>
-        <v>24045.0</v>
+        <v>14398.0</v>
       </c>
       <c r="Q9">
         <f>Q5+Q6+Q7</f>
-        <v>25637.0</v>
+        <v>15351.0</v>
       </c>
       <c r="R9">
         <f>R5+R6+R7</f>
-        <v>27334.0</v>
+        <v>16367.0</v>
       </c>
       <c r="S9">
         <f>S5+S6+S7</f>
-        <v>29144.0</v>
+        <v>17451.0</v>
       </c>
       <c r="T9">
         <f>T5+T6+T7</f>
-        <v>31074.0</v>
+        <v>18606.0</v>
       </c>
       <c r="U9">
         <f>U5+U6+U7</f>
-        <v>33131.0</v>
+        <v>19838.0</v>
       </c>
       <c r="V9">
         <f>V5+V6+V7</f>
-        <v>35325.0</v>
+        <v>21152.0</v>
       </c>
       <c r="W9">
         <f>W5+W6+W7</f>
-        <v>37664.0</v>
+        <v>22552.0</v>
       </c>
       <c r="X9">
         <f>X5+X6+X7</f>
-        <v>40157.0</v>
+        <v>24045.0</v>
       </c>
       <c r="Y9">
         <f>Y5+Y6+Y7</f>
-        <v>42815.0</v>
+        <v>25637.0</v>
       </c>
       <c r="Z9">
         <f>Z5+Z6+Z7</f>
-        <v>45649.0</v>
+        <v>27334.0</v>
       </c>
     </row>
     <row r="11">
@@ -1276,67 +1275,67 @@
       </c>
       <c r="K13">
         <f>ROUND((K5+K9)/2,0)</f>
-        <v>16909.0</v>
+        <v>10125.0</v>
       </c>
       <c r="L13">
         <f>ROUND((L5+L9)/2,0)</f>
-        <v>18029.0</v>
+        <v>10795.0</v>
       </c>
       <c r="M13">
         <f>ROUND((M5+M9)/2,0)</f>
-        <v>19222.0</v>
+        <v>11510.0</v>
       </c>
       <c r="N13">
         <f>ROUND((N5+N9)/2,0)</f>
-        <v>20495.0</v>
+        <v>12273.0</v>
       </c>
       <c r="O13">
         <f>ROUND((O5+O9)/2,0)</f>
-        <v>21852.0</v>
+        <v>13085.0</v>
       </c>
       <c r="P13">
         <f>ROUND((P5+P9)/2,0)</f>
-        <v>23299.0</v>
+        <v>13951.0</v>
       </c>
       <c r="Q13">
         <f>ROUND((Q5+Q9)/2,0)</f>
-        <v>24841.0</v>
+        <v>14875.0</v>
       </c>
       <c r="R13">
         <f>ROUND((R5+R9)/2,0)</f>
-        <v>26486.0</v>
+        <v>15859.0</v>
       </c>
       <c r="S13">
         <f>ROUND((S5+S9)/2,0)</f>
-        <v>28239.0</v>
+        <v>16909.0</v>
       </c>
       <c r="T13">
         <f>ROUND((T5+T9)/2,0)</f>
-        <v>30109.0</v>
+        <v>18029.0</v>
       </c>
       <c r="U13">
         <f>ROUND((U5+U9)/2,0)</f>
-        <v>32103.0</v>
+        <v>19222.0</v>
       </c>
       <c r="V13">
         <f>ROUND((V5+V9)/2,0)</f>
-        <v>34228.0</v>
+        <v>20495.0</v>
       </c>
       <c r="W13">
         <f>ROUND((W5+W9)/2,0)</f>
-        <v>36495.0</v>
+        <v>21852.0</v>
       </c>
       <c r="X13">
         <f>ROUND((X5+X9)/2,0)</f>
-        <v>38911.0</v>
+        <v>23299.0</v>
       </c>
       <c r="Y13">
         <f>ROUND((Y5+Y9)/2,0)</f>
-        <v>41486.0</v>
+        <v>24841.0</v>
       </c>
       <c r="Z13">
         <f>ROUND((Z5+Z9)/2,0)</f>
-        <v>44232.0</v>
+        <v>26486.0</v>
       </c>
     </row>
     <row r="15">
@@ -1379,67 +1378,67 @@
       </c>
       <c r="K15">
         <f>ROUND(K13*K11,0)</f>
-        <v>1547681.0</v>
+        <v>926741.0</v>
       </c>
       <c r="L15">
         <f>ROUND(L13*L11,0)</f>
-        <v>1666240.0</v>
+        <v>997674.0</v>
       </c>
       <c r="M15">
         <f>ROUND(M13*M11,0)</f>
-        <v>1793797.0</v>
+        <v>1074113.0</v>
       </c>
       <c r="N15">
         <f>ROUND(N13*N11,0)</f>
-        <v>1931244.0</v>
+        <v>1156485.0</v>
       </c>
       <c r="O15">
         <f>ROUND(O13*O11,0)</f>
-        <v>2078999.0</v>
+        <v>1244907.0</v>
       </c>
       <c r="P15">
         <f>ROUND(P13*P11,0)</f>
-        <v>2238102.0</v>
+        <v>1340133.0</v>
       </c>
       <c r="Q15">
         <f>ROUND(Q13*Q11,0)</f>
-        <v>2409329.0</v>
+        <v>1442726.0</v>
       </c>
       <c r="R15">
         <f>ROUND(R13*R11,0)</f>
-        <v>2593774.0</v>
+        <v>1553072.0</v>
       </c>
       <c r="S15">
         <f>ROUND(S13*S11,0)</f>
-        <v>2792272.0</v>
+        <v>1671962.0</v>
       </c>
       <c r="T15">
         <f>ROUND(T13*T11,0)</f>
-        <v>3006083.0</v>
+        <v>1800015.0</v>
       </c>
       <c r="U15">
         <f>ROUND(U13*U11,0)</f>
-        <v>3236303.0</v>
+        <v>1937770.0</v>
       </c>
       <c r="V15">
         <f>ROUND(V13*V11,0)</f>
-        <v>3484068.0</v>
+        <v>2086186.0</v>
       </c>
       <c r="W15">
         <f>ROUND(W13*W11,0)</f>
-        <v>3750956.0</v>
+        <v>2245949.0</v>
       </c>
       <c r="X15">
         <f>ROUND(X13*X11,0)</f>
-        <v>4038184.0</v>
+        <v>2417970.0</v>
       </c>
       <c r="Y15">
         <f>ROUND(Y13*Y11,0)</f>
-        <v>4347318.0</v>
+        <v>2603088.0</v>
       </c>
       <c r="Z15">
         <f>ROUND(Z13*Z11,0)</f>
-        <v>4680188.0</v>
+        <v>2802484.0</v>
       </c>
     </row>
     <row r="17">
@@ -1482,67 +1481,67 @@
       </c>
       <c r="K17">
         <f>J17+K15</f>
-        <v>10559784.0</v>
+        <v>9938844.0</v>
       </c>
       <c r="L17">
         <f>K17+L15</f>
-        <v>12226024.0</v>
+        <v>10936518.0</v>
       </c>
       <c r="M17">
         <f>L17+M15</f>
-        <v>14019821.0</v>
+        <v>12010631.0</v>
       </c>
       <c r="N17">
         <f>M17+N15</f>
-        <v>15951065.0</v>
+        <v>13167116.0</v>
       </c>
       <c r="O17">
         <f>N17+O15</f>
-        <v>18030064.0</v>
+        <v>14412023.0</v>
       </c>
       <c r="P17">
         <f>O17+P15</f>
-        <v>20268166.0</v>
+        <v>15752156.0</v>
       </c>
       <c r="Q17">
         <f>P17+Q15</f>
-        <v>22677495.0</v>
+        <v>17194882.0</v>
       </c>
       <c r="R17">
         <f>Q17+R15</f>
-        <v>25271269.0</v>
+        <v>18747954.0</v>
       </c>
       <c r="S17">
         <f>R17+S15</f>
-        <v>28063541.0</v>
+        <v>20419916.0</v>
       </c>
       <c r="T17">
         <f>S17+T15</f>
-        <v>31069624.0</v>
+        <v>22219931.0</v>
       </c>
       <c r="U17">
         <f>T17+U15</f>
-        <v>34305927.0</v>
+        <v>24157701.0</v>
       </c>
       <c r="V17">
         <f>U17+V15</f>
-        <v>37789995.0</v>
+        <v>26243887.0</v>
       </c>
       <c r="W17">
         <f>V17+W15</f>
-        <v>41540951.0</v>
+        <v>28489836.0</v>
       </c>
       <c r="X17">
         <f>W17+X15</f>
-        <v>45579135.0</v>
+        <v>30907806.0</v>
       </c>
       <c r="Y17">
         <f>X17+Y15</f>
-        <v>49926453.0</v>
+        <v>33510894.0</v>
       </c>
       <c r="Z17">
         <f>Y17+Z15</f>
-        <v>54606641.0</v>
+        <v>36313378.0</v>
       </c>
     </row>
   </sheetData>
@@ -2121,67 +2120,67 @@
       </c>
       <c r="K10">
         <f>ROUND(Revenue!K15*Assumptions!$B$11,0)</f>
-        <v>285083.0</v>
+        <v>170706.0</v>
       </c>
       <c r="L10">
         <f>ROUND(Revenue!L15*Assumptions!$B$11,0)</f>
-        <v>306921.0</v>
+        <v>183772.0</v>
       </c>
       <c r="M10">
         <f>ROUND(Revenue!M15*Assumptions!$B$11,0)</f>
-        <v>330417.0</v>
+        <v>197852.0</v>
       </c>
       <c r="N10">
         <f>ROUND(Revenue!N15*Assumptions!$B$11,0)</f>
-        <v>355735.0</v>
+        <v>213025.0</v>
       </c>
       <c r="O10">
         <f>ROUND(Revenue!O15*Assumptions!$B$11,0)</f>
-        <v>382952.0</v>
+        <v>229312.0</v>
       </c>
       <c r="P10">
         <f>ROUND(Revenue!P15*Assumptions!$B$11,0)</f>
-        <v>412258.0</v>
+        <v>246852.0</v>
       </c>
       <c r="Q10">
         <f>ROUND(Revenue!Q15*Assumptions!$B$11,0)</f>
-        <v>443798.0</v>
+        <v>265750.0</v>
       </c>
       <c r="R10">
         <f>ROUND(Revenue!R15*Assumptions!$B$11,0)</f>
-        <v>477773.0</v>
+        <v>286076.0</v>
       </c>
       <c r="S10">
         <f>ROUND(Revenue!S15*Assumptions!$B$11,0)</f>
-        <v>514337.0</v>
+        <v>307975.0</v>
       </c>
       <c r="T10">
         <f>ROUND(Revenue!T15*Assumptions!$B$11,0)</f>
-        <v>553720.0</v>
+        <v>331563.0</v>
       </c>
       <c r="U10">
         <f>ROUND(Revenue!U15*Assumptions!$B$11,0)</f>
-        <v>596127.0</v>
+        <v>356937.0</v>
       </c>
       <c r="V10">
         <f>ROUND(Revenue!V15*Assumptions!$B$11,0)</f>
-        <v>641765.0</v>
+        <v>384275.0</v>
       </c>
       <c r="W10">
         <f>ROUND(Revenue!W15*Assumptions!$B$11,0)</f>
-        <v>690926.0</v>
+        <v>413704.0</v>
       </c>
       <c r="X10">
         <f>ROUND(Revenue!X15*Assumptions!$B$11,0)</f>
-        <v>743833.0</v>
+        <v>445390.0</v>
       </c>
       <c r="Y10">
         <f>ROUND(Revenue!Y15*Assumptions!$B$11,0)</f>
-        <v>800776.0</v>
+        <v>479489.0</v>
       </c>
       <c r="Z10">
         <f>ROUND(Revenue!Z15*Assumptions!$B$11,0)</f>
-        <v>862091.0</v>
+        <v>516218.0</v>
       </c>
     </row>
     <row r="11">
@@ -2224,67 +2223,67 @@
       </c>
       <c r="K11">
         <f>ROUND(Revenue!K15*Assumptions!$B$16,0)</f>
-        <v>213425.0</v>
+        <v>127798.0</v>
       </c>
       <c r="L11">
         <f>ROUND(Revenue!L15*Assumptions!$B$16,0)</f>
-        <v>229774.0</v>
+        <v>137579.0</v>
       </c>
       <c r="M11">
         <f>ROUND(Revenue!M15*Assumptions!$B$16,0)</f>
-        <v>247365.0</v>
+        <v>148120.0</v>
       </c>
       <c r="N11">
         <f>ROUND(Revenue!N15*Assumptions!$B$16,0)</f>
-        <v>266319.0</v>
+        <v>159479.0</v>
       </c>
       <c r="O11">
         <f>ROUND(Revenue!O15*Assumptions!$B$16,0)</f>
-        <v>286694.0</v>
+        <v>171673.0</v>
       </c>
       <c r="P11">
         <f>ROUND(Revenue!P15*Assumptions!$B$16,0)</f>
-        <v>308634.0</v>
+        <v>184804.0</v>
       </c>
       <c r="Q11">
         <f>ROUND(Revenue!Q15*Assumptions!$B$16,0)</f>
-        <v>332246.0</v>
+        <v>198952.0</v>
       </c>
       <c r="R11">
         <f>ROUND(Revenue!R15*Assumptions!$B$16,0)</f>
-        <v>357681.0</v>
+        <v>214169.0</v>
       </c>
       <c r="S11">
         <f>ROUND(Revenue!S15*Assumptions!$B$16,0)</f>
-        <v>385054.0</v>
+        <v>230564.0</v>
       </c>
       <c r="T11">
         <f>ROUND(Revenue!T15*Assumptions!$B$16,0)</f>
-        <v>414539.0</v>
+        <v>248222.0</v>
       </c>
       <c r="U11">
         <f>ROUND(Revenue!U15*Assumptions!$B$16,0)</f>
-        <v>446286.0</v>
+        <v>267218.0</v>
       </c>
       <c r="V11">
         <f>ROUND(Revenue!V15*Assumptions!$B$16,0)</f>
-        <v>480453.0</v>
+        <v>287685.0</v>
       </c>
       <c r="W11">
         <f>ROUND(Revenue!W15*Assumptions!$B$16,0)</f>
-        <v>517257.0</v>
+        <v>309716.0</v>
       </c>
       <c r="X11">
         <f>ROUND(Revenue!X15*Assumptions!$B$16,0)</f>
-        <v>556866.0</v>
+        <v>333438.0</v>
       </c>
       <c r="Y11">
         <f>ROUND(Revenue!Y15*Assumptions!$B$16,0)</f>
-        <v>599495.0</v>
+        <v>358966.0</v>
       </c>
       <c r="Z11">
         <f>ROUND(Revenue!Z15*Assumptions!$B$16,0)</f>
-        <v>645398.0</v>
+        <v>386463.0</v>
       </c>
     </row>
     <row r="12">
@@ -2430,67 +2429,67 @@
       </c>
       <c r="K14">
         <f>K8+K10+K11+K12</f>
-        <v>824896.0</v>
+        <v>624892.0</v>
       </c>
       <c r="L14">
         <f>L8+L10+L11+L12</f>
-        <v>878496.0</v>
+        <v>663152.0</v>
       </c>
       <c r="M14">
         <f>M8+M10+M11+M12</f>
-        <v>934997.0</v>
+        <v>703187.0</v>
       </c>
       <c r="N14">
         <f>N8+N10+N11+N12</f>
-        <v>994683.0</v>
+        <v>745133.0</v>
       </c>
       <c r="O14">
         <f>O8+O10+O11+O12</f>
-        <v>1057689.0</v>
+        <v>789028.0</v>
       </c>
       <c r="P14">
         <f>P8+P10+P11+P12</f>
-        <v>1124349.0</v>
+        <v>835113.0</v>
       </c>
       <c r="Q14">
         <f>Q8+Q10+Q11+Q12</f>
-        <v>1194917.0</v>
+        <v>883575.0</v>
       </c>
       <c r="R14">
         <f>R8+R10+R11+R12</f>
-        <v>1269742.0</v>
+        <v>934533.0</v>
       </c>
       <c r="S14">
         <f>S8+S10+S11+S12</f>
-        <v>1349095.0</v>
+        <v>988243.0</v>
       </c>
       <c r="T14">
         <f>T8+T10+T11+T12</f>
-        <v>1433379.0</v>
+        <v>1044905.0</v>
       </c>
       <c r="U14">
         <f>U8+U10+U11+U12</f>
-        <v>1522950.0</v>
+        <v>1104692.0</v>
       </c>
       <c r="V14">
         <f>V8+V10+V11+V12</f>
-        <v>1618172.0</v>
+        <v>1167914.0</v>
       </c>
       <c r="W14">
         <f>W8+W10+W11+W12</f>
-        <v>1719554.0</v>
+        <v>1234791.0</v>
       </c>
       <c r="X14">
         <f>X8+X10+X11+X12</f>
-        <v>1827487.0</v>
+        <v>1305616.0</v>
       </c>
       <c r="Y14">
         <f>Y8+Y10+Y11+Y12</f>
-        <v>1942478.0</v>
+        <v>1380662.0</v>
       </c>
       <c r="Z14">
         <f>Z8+Z10+Z11+Z12</f>
-        <v>2065114.0</v>
+        <v>1460306.0</v>
       </c>
     </row>
   </sheetData>
@@ -2662,71 +2661,71 @@
       </c>
       <c r="K5">
         <f>Revenue!K15</f>
-        <v>1547681.0</v>
+        <v>926741.0</v>
       </c>
       <c r="L5">
         <f>Revenue!L15</f>
-        <v>1666240.0</v>
+        <v>997674.0</v>
       </c>
       <c r="M5">
         <f>Revenue!M15</f>
-        <v>1793797.0</v>
+        <v>1074113.0</v>
       </c>
       <c r="N5">
         <f>Revenue!N15</f>
-        <v>1931244.0</v>
+        <v>1156485.0</v>
       </c>
       <c r="O5">
         <f>Revenue!O15</f>
-        <v>2078999.0</v>
+        <v>1244907.0</v>
       </c>
       <c r="P5">
         <f>Revenue!P15</f>
-        <v>2238102.0</v>
+        <v>1340133.0</v>
       </c>
       <c r="Q5">
         <f>Revenue!Q15</f>
-        <v>2409329.0</v>
+        <v>1442726.0</v>
       </c>
       <c r="R5">
         <f>Revenue!R15</f>
-        <v>2593774.0</v>
+        <v>1553072.0</v>
       </c>
       <c r="S5">
         <f>Revenue!S15</f>
-        <v>2792272.0</v>
+        <v>1671962.0</v>
       </c>
       <c r="T5">
         <f>Revenue!T15</f>
-        <v>3006083.0</v>
+        <v>1800015.0</v>
       </c>
       <c r="U5">
         <f>Revenue!U15</f>
-        <v>3236303.0</v>
+        <v>1937770.0</v>
       </c>
       <c r="V5">
         <f>Revenue!V15</f>
-        <v>3484068.0</v>
+        <v>2086186.0</v>
       </c>
       <c r="W5">
         <f>Revenue!W15</f>
-        <v>3750956.0</v>
+        <v>2245949.0</v>
       </c>
       <c r="X5">
         <f>Revenue!X15</f>
-        <v>4038184.0</v>
+        <v>2417970.0</v>
       </c>
       <c r="Y5">
         <f>Revenue!Y15</f>
-        <v>4347318.0</v>
+        <v>2603088.0</v>
       </c>
       <c r="Z5">
         <f>Revenue!Z15</f>
-        <v>4680188.0</v>
+        <v>2802484.0</v>
       </c>
       <c r="AA5">
         <f>SUM(C5:Z5)</f>
-        <v>54606641.0</v>
+        <v>36313378.0</v>
       </c>
     </row>
     <row r="6">
@@ -2769,71 +2768,71 @@
       </c>
       <c r="K6">
         <f>-Costs!K10</f>
-        <v>-285083.0</v>
+        <v>-170706.0</v>
       </c>
       <c r="L6">
         <f>-Costs!L10</f>
-        <v>-306921.0</v>
+        <v>-183772.0</v>
       </c>
       <c r="M6">
         <f>-Costs!M10</f>
-        <v>-330417.0</v>
+        <v>-197852.0</v>
       </c>
       <c r="N6">
         <f>-Costs!N10</f>
-        <v>-355735.0</v>
+        <v>-213025.0</v>
       </c>
       <c r="O6">
         <f>-Costs!O10</f>
-        <v>-382952.0</v>
+        <v>-229312.0</v>
       </c>
       <c r="P6">
         <f>-Costs!P10</f>
-        <v>-412258.0</v>
+        <v>-246852.0</v>
       </c>
       <c r="Q6">
         <f>-Costs!Q10</f>
-        <v>-443798.0</v>
+        <v>-265750.0</v>
       </c>
       <c r="R6">
         <f>-Costs!R10</f>
-        <v>-477773.0</v>
+        <v>-286076.0</v>
       </c>
       <c r="S6">
         <f>-Costs!S10</f>
-        <v>-514337.0</v>
+        <v>-307975.0</v>
       </c>
       <c r="T6">
         <f>-Costs!T10</f>
-        <v>-553720.0</v>
+        <v>-331563.0</v>
       </c>
       <c r="U6">
         <f>-Costs!U10</f>
-        <v>-596127.0</v>
+        <v>-356937.0</v>
       </c>
       <c r="V6">
         <f>-Costs!V10</f>
-        <v>-641765.0</v>
+        <v>-384275.0</v>
       </c>
       <c r="W6">
         <f>-Costs!W10</f>
-        <v>-690926.0</v>
+        <v>-413704.0</v>
       </c>
       <c r="X6">
         <f>-Costs!X10</f>
-        <v>-743833.0</v>
+        <v>-445390.0</v>
       </c>
       <c r="Y6">
         <f>-Costs!Y10</f>
-        <v>-800776.0</v>
+        <v>-479489.0</v>
       </c>
       <c r="Z6">
         <f>-Costs!Z10</f>
-        <v>-862091.0</v>
+        <v>-516218.0</v>
       </c>
       <c r="AA6">
         <f>SUM(C6:Z6)</f>
-        <v>-10058541.0</v>
+        <v>-6688925.0</v>
       </c>
     </row>
     <row r="7">
@@ -2876,71 +2875,71 @@
       </c>
       <c r="K7">
         <f>K5+K6</f>
-        <v>1262598.0</v>
+        <v>756035.0</v>
       </c>
       <c r="L7">
         <f>L5+L6</f>
-        <v>1359319.0</v>
+        <v>813902.0</v>
       </c>
       <c r="M7">
         <f>M5+M6</f>
-        <v>1463380.0</v>
+        <v>876261.0</v>
       </c>
       <c r="N7">
         <f>N5+N6</f>
-        <v>1575509.0</v>
+        <v>943460.0</v>
       </c>
       <c r="O7">
         <f>O5+O6</f>
-        <v>1696047.0</v>
+        <v>1015595.0</v>
       </c>
       <c r="P7">
         <f>P5+P6</f>
-        <v>1825844.0</v>
+        <v>1093281.0</v>
       </c>
       <c r="Q7">
         <f>Q5+Q6</f>
-        <v>1965531.0</v>
+        <v>1176976.0</v>
       </c>
       <c r="R7">
         <f>R5+R6</f>
-        <v>2116001.0</v>
+        <v>1266996.0</v>
       </c>
       <c r="S7">
         <f>S5+S6</f>
-        <v>2277935.0</v>
+        <v>1363987.0</v>
       </c>
       <c r="T7">
         <f>T5+T6</f>
-        <v>2452363.0</v>
+        <v>1468452.0</v>
       </c>
       <c r="U7">
         <f>U5+U6</f>
-        <v>2640176.0</v>
+        <v>1580833.0</v>
       </c>
       <c r="V7">
         <f>V5+V6</f>
-        <v>2842303.0</v>
+        <v>1701911.0</v>
       </c>
       <c r="W7">
         <f>W5+W6</f>
-        <v>3060030.0</v>
+        <v>1832245.0</v>
       </c>
       <c r="X7">
         <f>X5+X6</f>
-        <v>3294351.0</v>
+        <v>1972580.0</v>
       </c>
       <c r="Y7">
         <f>Y5+Y6</f>
-        <v>3546542.0</v>
+        <v>2123599.0</v>
       </c>
       <c r="Z7">
         <f>Z5+Z6</f>
-        <v>3818097.0</v>
+        <v>2286266.0</v>
       </c>
       <c r="AA7">
         <f>SUM(C7:Z7)</f>
-        <v>44548100.0</v>
+        <v>29624453.0</v>
       </c>
     </row>
     <row r="8">
@@ -3193,71 +3192,71 @@
       </c>
       <c r="K11">
         <f>-Costs!K11</f>
-        <v>-213425.0</v>
+        <v>-127798.0</v>
       </c>
       <c r="L11">
         <f>-Costs!L11</f>
-        <v>-229774.0</v>
+        <v>-137579.0</v>
       </c>
       <c r="M11">
         <f>-Costs!M11</f>
-        <v>-247365.0</v>
+        <v>-148120.0</v>
       </c>
       <c r="N11">
         <f>-Costs!N11</f>
-        <v>-266319.0</v>
+        <v>-159479.0</v>
       </c>
       <c r="O11">
         <f>-Costs!O11</f>
-        <v>-286694.0</v>
+        <v>-171673.0</v>
       </c>
       <c r="P11">
         <f>-Costs!P11</f>
-        <v>-308634.0</v>
+        <v>-184804.0</v>
       </c>
       <c r="Q11">
         <f>-Costs!Q11</f>
-        <v>-332246.0</v>
+        <v>-198952.0</v>
       </c>
       <c r="R11">
         <f>-Costs!R11</f>
-        <v>-357681.0</v>
+        <v>-214169.0</v>
       </c>
       <c r="S11">
         <f>-Costs!S11</f>
-        <v>-385054.0</v>
+        <v>-230564.0</v>
       </c>
       <c r="T11">
         <f>-Costs!T11</f>
-        <v>-414539.0</v>
+        <v>-248222.0</v>
       </c>
       <c r="U11">
         <f>-Costs!U11</f>
-        <v>-446286.0</v>
+        <v>-267218.0</v>
       </c>
       <c r="V11">
         <f>-Costs!V11</f>
-        <v>-480453.0</v>
+        <v>-287685.0</v>
       </c>
       <c r="W11">
         <f>-Costs!W11</f>
-        <v>-517257.0</v>
+        <v>-309716.0</v>
       </c>
       <c r="X11">
         <f>-Costs!X11</f>
-        <v>-556866.0</v>
+        <v>-333438.0</v>
       </c>
       <c r="Y11">
         <f>-Costs!Y11</f>
-        <v>-599495.0</v>
+        <v>-358966.0</v>
       </c>
       <c r="Z11">
         <f>-Costs!Z11</f>
-        <v>-645398.0</v>
+        <v>-386463.0</v>
       </c>
       <c r="AA11">
         <f>SUM(C11:Z11)</f>
-        <v>-7530254.0</v>
+        <v>-5007614.0</v>
       </c>
     </row>
     <row r="12">
@@ -3407,71 +3406,71 @@
       </c>
       <c r="K13">
         <f>K10+K11+K12</f>
-        <v>-539813.0</v>
+        <v>-454186.0</v>
       </c>
       <c r="L13">
         <f>L10+L11+L12</f>
-        <v>-571575.0</v>
+        <v>-479380.0</v>
       </c>
       <c r="M13">
         <f>M10+M11+M12</f>
-        <v>-604580.0</v>
+        <v>-505335.0</v>
       </c>
       <c r="N13">
         <f>N10+N11+N12</f>
-        <v>-638948.0</v>
+        <v>-532108.0</v>
       </c>
       <c r="O13">
         <f>O10+O11+O12</f>
-        <v>-674737.0</v>
+        <v>-559716.0</v>
       </c>
       <c r="P13">
         <f>P10+P11+P12</f>
-        <v>-712091.0</v>
+        <v>-588261.0</v>
       </c>
       <c r="Q13">
         <f>Q10+Q11+Q12</f>
-        <v>-751119.0</v>
+        <v>-617825.0</v>
       </c>
       <c r="R13">
         <f>R10+R11+R12</f>
-        <v>-791969.0</v>
+        <v>-648457.0</v>
       </c>
       <c r="S13">
         <f>S10+S11+S12</f>
-        <v>-834758.0</v>
+        <v>-680268.0</v>
       </c>
       <c r="T13">
         <f>T10+T11+T12</f>
-        <v>-879659.0</v>
+        <v>-713342.0</v>
       </c>
       <c r="U13">
         <f>U10+U11+U12</f>
-        <v>-926823.0</v>
+        <v>-747755.0</v>
       </c>
       <c r="V13">
         <f>V10+V11+V12</f>
-        <v>-976407.0</v>
+        <v>-783639.0</v>
       </c>
       <c r="W13">
         <f>W10+W11+W12</f>
-        <v>-1028628.0</v>
+        <v>-821087.0</v>
       </c>
       <c r="X13">
         <f>X10+X11+X12</f>
-        <v>-1083654.0</v>
+        <v>-860226.0</v>
       </c>
       <c r="Y13">
         <f>Y10+Y11+Y12</f>
-        <v>-1141702.0</v>
+        <v>-901173.0</v>
       </c>
       <c r="Z13">
         <f>Z10+Z11+Z12</f>
-        <v>-1203023.0</v>
+        <v>-944088.0</v>
       </c>
       <c r="AA13">
         <f>SUM(C13:Z13)</f>
-        <v>-16658528.0</v>
+        <v>-14135888.0</v>
       </c>
     </row>
     <row r="15">
@@ -3514,71 +3513,71 @@
       </c>
       <c r="K15">
         <f>K7+K13</f>
-        <v>722785.0</v>
+        <v>301849.0</v>
       </c>
       <c r="L15">
         <f>L7+L13</f>
-        <v>787744.0</v>
+        <v>334522.0</v>
       </c>
       <c r="M15">
         <f>M7+M13</f>
-        <v>858800.0</v>
+        <v>370926.0</v>
       </c>
       <c r="N15">
         <f>N7+N13</f>
-        <v>936561.0</v>
+        <v>411352.0</v>
       </c>
       <c r="O15">
         <f>O7+O13</f>
-        <v>1021310.0</v>
+        <v>455879.0</v>
       </c>
       <c r="P15">
         <f>P7+P13</f>
-        <v>1113753.0</v>
+        <v>505020.0</v>
       </c>
       <c r="Q15">
         <f>Q7+Q13</f>
-        <v>1214412.0</v>
+        <v>559151.0</v>
       </c>
       <c r="R15">
         <f>R7+R13</f>
-        <v>1324032.0</v>
+        <v>618539.0</v>
       </c>
       <c r="S15">
         <f>S7+S13</f>
-        <v>1443177.0</v>
+        <v>683719.0</v>
       </c>
       <c r="T15">
         <f>T7+T13</f>
-        <v>1572704.0</v>
+        <v>755110.0</v>
       </c>
       <c r="U15">
         <f>U7+U13</f>
-        <v>1713353.0</v>
+        <v>833078.0</v>
       </c>
       <c r="V15">
         <f>V7+V13</f>
-        <v>1865896.0</v>
+        <v>918272.0</v>
       </c>
       <c r="W15">
         <f>W7+W13</f>
-        <v>2031402.0</v>
+        <v>1011158.0</v>
       </c>
       <c r="X15">
         <f>X7+X13</f>
-        <v>2210697.0</v>
+        <v>1112354.0</v>
       </c>
       <c r="Y15">
         <f>Y7+Y13</f>
-        <v>2404840.0</v>
+        <v>1222426.0</v>
       </c>
       <c r="Z15">
         <f>Z7+Z13</f>
-        <v>2615074.0</v>
+        <v>1342178.0</v>
       </c>
       <c r="AA15">
         <f>SUM(C15:Z15)</f>
-        <v>27889572.0</v>
+        <v>15488565.0</v>
       </c>
     </row>
     <row r="16">
@@ -3621,67 +3620,67 @@
       </c>
       <c r="K16">
         <f>IF(K5=0,0,ROUND(K15/K5,4))</f>
-        <v>0.467</v>
+        <v>0.3257</v>
       </c>
       <c r="L16">
         <f>IF(L5=0,0,ROUND(L15/L5,4))</f>
-        <v>0.4728</v>
+        <v>0.3353</v>
       </c>
       <c r="M16">
         <f>IF(M5=0,0,ROUND(M15/M5,4))</f>
-        <v>0.4788</v>
+        <v>0.3453</v>
       </c>
       <c r="N16">
         <f>IF(N5=0,0,ROUND(N15/N5,4))</f>
-        <v>0.485</v>
+        <v>0.3557</v>
       </c>
       <c r="O16">
         <f>IF(O5=0,0,ROUND(O15/O5,4))</f>
-        <v>0.4913</v>
+        <v>0.3662</v>
       </c>
       <c r="P16">
         <f>IF(P5=0,0,ROUND(P15/P5,4))</f>
-        <v>0.4976</v>
+        <v>0.3768</v>
       </c>
       <c r="Q16">
         <f>IF(Q5=0,0,ROUND(Q15/Q5,4))</f>
-        <v>0.504</v>
+        <v>0.3876</v>
       </c>
       <c r="R16">
         <f>IF(R5=0,0,ROUND(R15/R5,4))</f>
-        <v>0.5105</v>
+        <v>0.3983</v>
       </c>
       <c r="S16">
         <f>IF(S5=0,0,ROUND(S15/S5,4))</f>
-        <v>0.5168</v>
+        <v>0.4089</v>
       </c>
       <c r="T16">
         <f>IF(T5=0,0,ROUND(T15/T5,4))</f>
-        <v>0.5232</v>
+        <v>0.4195</v>
       </c>
       <c r="U16">
         <f>IF(U5=0,0,ROUND(U15/U5,4))</f>
-        <v>0.5294</v>
+        <v>0.4299</v>
       </c>
       <c r="V16">
         <f>IF(V5=0,0,ROUND(V15/V5,4))</f>
-        <v>0.5356</v>
+        <v>0.4402</v>
       </c>
       <c r="W16">
         <f>IF(W5=0,0,ROUND(W15/W5,4))</f>
-        <v>0.5416</v>
+        <v>0.4502</v>
       </c>
       <c r="X16">
         <f>IF(X5=0,0,ROUND(X15/X5,4))</f>
-        <v>0.5474</v>
+        <v>0.46</v>
       </c>
       <c r="Y16">
         <f>IF(Y5=0,0,ROUND(Y15/Y5,4))</f>
-        <v>0.5532</v>
+        <v>0.4696</v>
       </c>
       <c r="Z16">
         <f>IF(Z5=0,0,ROUND(Z15/Z5,4))</f>
-        <v>0.5588</v>
+        <v>0.4789</v>
       </c>
     </row>
     <row r="18">
@@ -3724,67 +3723,67 @@
       </c>
       <c r="K18">
         <f>J18+K15</f>
-        <v>4775817.0</v>
+        <v>4354881.0</v>
       </c>
       <c r="L18">
         <f>K18+L15</f>
-        <v>5563561.0</v>
+        <v>4689403.0</v>
       </c>
       <c r="M18">
         <f>L18+M15</f>
-        <v>6422361.0</v>
+        <v>5060329.0</v>
       </c>
       <c r="N18">
         <f>M18+N15</f>
-        <v>7358922.0</v>
+        <v>5471681.0</v>
       </c>
       <c r="O18">
         <f>N18+O15</f>
-        <v>8380232.0</v>
+        <v>5927560.0</v>
       </c>
       <c r="P18">
         <f>O18+P15</f>
-        <v>9493985.0</v>
+        <v>6432580.0</v>
       </c>
       <c r="Q18">
         <f>P18+Q15</f>
-        <v>10708397.0</v>
+        <v>6991731.0</v>
       </c>
       <c r="R18">
         <f>Q18+R15</f>
-        <v>12032429.0</v>
+        <v>7610270.0</v>
       </c>
       <c r="S18">
         <f>R18+S15</f>
-        <v>13475606.0</v>
+        <v>8293989.0</v>
       </c>
       <c r="T18">
         <f>S18+T15</f>
-        <v>15048310.0</v>
+        <v>9049099.0</v>
       </c>
       <c r="U18">
         <f>T18+U15</f>
-        <v>16761663.0</v>
+        <v>9882177.0</v>
       </c>
       <c r="V18">
         <f>U18+V15</f>
-        <v>18627559.0</v>
+        <v>10800449.0</v>
       </c>
       <c r="W18">
         <f>V18+W15</f>
-        <v>20658961.0</v>
+        <v>11811607.0</v>
       </c>
       <c r="X18">
         <f>W18+X15</f>
-        <v>22869658.0</v>
+        <v>12923961.0</v>
       </c>
       <c r="Y18">
         <f>X18+Y15</f>
-        <v>25274498.0</v>
+        <v>14146387.0</v>
       </c>
       <c r="Z18">
         <f>Y18+Z15</f>
-        <v>27889572.0</v>
+        <v>15488565.0</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3815,7 @@
       </c>
       <c r="B3">
         <f>Revenue!Z17</f>
-        <v>54606641.0</v>
+        <v>36313378.0</v>
       </c>
     </row>
     <row r="4">
@@ -3827,7 +3826,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>27889572.0</v>
+        <v>15488565.0</v>
       </c>
     </row>
     <row r="5">
@@ -3838,7 +3837,7 @@
       </c>
       <c r="B5">
         <f>SUM('P&amp;L'!O15:Z15)</f>
-        <v>20530650.0</v>
+        <v>10016884.0</v>
       </c>
     </row>
     <row r="6">
@@ -3860,7 +3859,7 @@
       </c>
       <c r="B7">
         <f>ROUND(B5*B6,0)</f>
-        <v>195041175.0</v>
+        <v>95160398.0</v>
       </c>
     </row>
     <row r="8">
@@ -3882,7 +3881,7 @@
       </c>
       <c r="B9">
         <f>B7-B8</f>
-        <v>191491175.0</v>
+        <v>91610398.0</v>
       </c>
     </row>
     <row r="11">
@@ -3893,7 +3892,7 @@
       </c>
       <c r="B11">
         <f>AVERAGE('P&amp;L'!C15:Z15)</f>
-        <v>1162065.5</v>
+        <v>645356.875</v>
       </c>
     </row>
     <row r="12">
@@ -3904,7 +3903,7 @@
       </c>
       <c r="B12">
         <f>MAX('P&amp;L'!C15:Z15)</f>
-        <v>2615074.0</v>
+        <v>1342178.0</v>
       </c>
     </row>
     <row r="13">
@@ -3915,7 +3914,7 @@
       </c>
       <c r="B13">
         <f>MIN('P&amp;L'!C15:Z15)</f>
-        <v>378468.0</v>
+        <v>301849.0</v>
       </c>
     </row>
     <row r="14">
@@ -3926,7 +3925,7 @@
       </c>
       <c r="B14">
         <f>SUMIF('P&amp;L'!C15:Z15,"&gt;0")</f>
-        <v>27889572.0</v>
+        <v>15488565.0</v>
       </c>
     </row>
     <row r="15">
@@ -3937,7 +3936,7 @@
       </c>
       <c r="B15">
         <f>ABS(B12-B13)</f>
-        <v>2236606.0</v>
+        <v>1040329.0</v>
       </c>
     </row>
   </sheetData>
